--- a/LvM_refed_TAGkinetics_hpAAs_SCFAs.xlsx
+++ b/LvM_refed_TAGkinetics_hpAAs_SCFAs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/boyuan/Desktop/Harvard/Research/Energy Metabolism Atlas/LvM_Refed_TAGkinetics_portalAAs_SCFAs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B796E61-BE9D-D747-922D-6084BB5E27DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC840B3C-921C-6948-AED1-BB76F10B038D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" activeTab="1" xr2:uid="{5E0D7404-E754-4442-97F6-BA3E5E250F0E}"/>
   </bookViews>
